--- a/processed_ruby_restored_xlsx/sc237_凛９：乳歯.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc237_凛９：乳歯.ss.xlsx
@@ -575,8 +575,8 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>She’s still pacing around, looking like she can’t calm
-down….</t>
+          <t>She’s still pacing around, looking like she can’t
+calm down….</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -744,8 +744,8 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Feeling pleased by that, I decided to go ahead and ask
-Miru-chan.</t>
+          <t>Feeling pleased by that, I decided to go ahead and
+ask Miru-chan.</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1670,8 +1670,8 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>But it doesn't seem to be just because Miru-chan and I
-forced her to look at it together...</t>
+          <t>But it doesn't seem to be just because Miru-chan and
+I forced her to look at it together...</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2842,8 +2842,8 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>「Hmm... If that's the case, shall I do it？ It's better
-than the dentist, right？」</t>
+          <t>「Hmm... If that's the case, shall I do it？ It's
+better than the dentist, right？」</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3391,8 +3391,8 @@
       <c r="B193" s="1" t="inlineStr">
         <is>
           <t>Whether she was scared of actually having a tooth
-pulled, or she could plainly see my ulterior motive...
-I don't know.</t>
+pulled, or she could plainly see my ulterior
+motive... I don't know.</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3482,8 +3482,8 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>Maybe the image of the dentist being scary is just too
-strong for her.</t>
+          <t>Maybe the image of the dentist being scary is just
+too strong for her.</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -4948,8 +4948,8 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>As if to hide her embarrassment, Rin-chan leans in and
-sucks at me.</t>
+          <t>As if to hide her embarrassment, Rin-chan leans in
+and sucks at me.</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -5132,8 +5132,8 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>I stimulate the surrounding teeth and gums, making her
-get more and more worked up.</t>
+          <t>I stimulate the surrounding teeth and gums, making
+her get more and more worked up.</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5424,7 +5424,8 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's face is totally melted, like she's in heat.</t>
+          <t>Rin-chan's face is totally melted, like she's in
+heat.</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5439,8 +5440,8 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>Her eyes are droopily glazed, and she keeps staring at
-me without letting go.</t>
+          <t>Her eyes are droopily glazed, and she keeps staring
+at me without letting go.</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5864,8 +5865,8 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>At this rate it would've started in the bathroom, so I
-picked Rin-chan up and ran.</t>
+          <t>At this rate it would've started in the bathroom, so
+I picked Rin-chan up and ran.</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -6079,8 +6080,8 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>With everyone together, Rin-chan is embarrassed to the
-max.</t>
+          <t>With everyone together, Rin-chan is embarrassed to
+the max.</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -6295,8 +6296,8 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>We sit on the bed, nod at each other, and go at it all
-at once...</t>
+          <t>We sit on the bed, nod at each other, and go at it
+all at once...</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6798,8 +6799,8 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t>Maybe because it was an insertion done on impulse, her
-pussy is clamping down hard.</t>
+          <t>Maybe because it was an insertion done on impulse,
+her pussy is clamping down hard.</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -7243,8 +7244,9 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>It was a far more melted expression than the one she'd
-had while we were kissing in the bathroom earlier.</t>
+          <t>It was a far more melted expression than the one
+she'd had while we were kissing in the bathroom
+earlier.</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7456,7 +7458,8 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>「Nn... chu！ Chu, chuu...！ Pwaa！ Ah... ah... Niini...！」</t>
+          <t>「Nn... chu！ Chu, chuu...！ Pwaa！ Ah... ah...
+Niini...！」</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7487,8 +7490,8 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t>She practically clings to my lips, soft enough to make
-them swell.</t>
+          <t>She practically clings to my lips, soft enough to
+make them swell.</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7610,8 +7613,8 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>But wanting to grant her wish too, I keep giving tiny,
-pecking kisses.</t>
+          <t>But wanting to grant her wish too, I keep giving
+tiny, pecking kisses.</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7964,8 +7967,8 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>Her wetness pours out, thick and sticky, and clings to
-my penis.</t>
+          <t>Her wetness pours out, thick and sticky, and clings
+to my penis.</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8331,8 +8334,8 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t>Still, it seems the stimulation is pretty intense, and
-Rin-chan lets out a muffled sound.</t>
+          <t>Still, it seems the stimulation is pretty intense,
+and Rin-chan lets out a muffled sound.</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -8639,9 +8642,9 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>Her mouth stays wide open, and the saliva leaking from
-the corners of her lips traces a slow glide down her
-jaw.</t>
+          <t>Her mouth stays wide open, and the saliva leaking
+from the corners of her lips traces a slow glide down
+her jaw.</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -8731,8 +8734,8 @@
       </c>
       <c r="B542" s="1" t="inlineStr">
         <is>
-          <t>「Weird spot？ Where could it be, I wonder…？ Maybe here,
-chup！ Chu！」</t>
+          <t>「Weird spot？ Where could it be, I wonder…？ Maybe
+here, chup！ Chu！」</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -9103,8 +9106,8 @@
       </c>
       <c r="B566" s="1" t="inlineStr">
         <is>
-          <t>Hearing words like that, even the penis gets even more
-excited...！</t>
+          <t>Hearing words like that, even the penis gets even
+more excited...！</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -9149,8 +9152,8 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>When my penis arched up hard inside her, she responded
-exactly as it should...</t>
+          <t>When my penis arched up hard inside her, she
+responded exactly as it should...</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9180,8 +9183,8 @@
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
-          <t>「Ahh！ Hah！ Huh！ Rin-chan！ You're... feeling it for me,
-right？」</t>
+          <t>「Ahh！ Hah！ Huh！ Rin-chan！ You're... feeling it for
+me, right？」</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -9259,8 +9262,8 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>If you feel that, is it only natural that you'd end up
-wanting to move more...？</t>
+          <t>If you feel that, is it only natural that you'd end
+up wanting to move more...？</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -9645,8 +9648,8 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>My excitement rides high as I call Rin-chan’s name and
-keep asking for more.</t>
+          <t>My excitement rides high as I call Rin-chan’s name
+and keep asking for more.</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -9707,8 +9710,8 @@
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
-          <t>「Hawafu！ It feels so good…！ It feels so good… fuwaaah,
-haa！」</t>
+          <t>「Hawafu！ It feels so good…！ It feels so good…
+fuwaaah, haa！」</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -9892,8 +9895,8 @@
       </c>
       <c r="B617" s="1" t="inlineStr">
         <is>
-          <t>Once I feel that, I get so wildly aroused I can't hold
-back！</t>
+          <t>Once I feel that, I get so wildly aroused I can't
+hold back！</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -10265,8 +10268,8 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>The penis was more honest about wanting to express its
-feelings, and an accidental eruption was
+          <t>The penis was more honest about wanting to express
+its feelings, and an accidental eruption was
 unavoidable...！</t>
         </is>
       </c>
@@ -11200,8 +11203,8 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>Just when I thought Rin-chan had suddenly shouted, she
-opened her mouth wide and let her tongue loll out
+          <t>Just when I thought Rin-chan had suddenly shouted,
+she opened her mouth wide and let her tongue loll out
 lazily.</t>
         </is>
       </c>
@@ -11323,8 +11326,8 @@
       </c>
       <c r="B710" s="1" t="inlineStr">
         <is>
-          <t>When I took out the case I'd prepared, Rin-chan placed
-the baby tooth inside it.</t>
+          <t>When I took out the case I'd prepared, Rin-chan
+placed the baby tooth inside it.</t>
         </is>
       </c>
       <c r="C710" t="n">
@@ -12085,8 +12088,8 @@
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>「Well, I think it's fine for now, but tell me again if
-you feel like it's about to come out.」</t>
+          <t>「Well, I think it's fine for now, but tell me again
+if you feel like it's about to come out.」</t>
         </is>
       </c>
       <c r="C760" t="n">

--- a/processed_ruby_restored_xlsx/sc237_凛９：乳歯.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc237_凛９：乳歯.ss.xlsx
@@ -559,8 +559,9 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>She keeps putting her hands to her face, especially
-her cheeks, and pressing them repeatedly.</t>
+          <t>They keep putting their hands to their face,
+especially their cheeks, and pressing them
+repeatedly.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -575,8 +576,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>She’s still pacing around, looking like she can’t
-calm down….</t>
+          <t>He’s still pacing around like he can’t calm down….</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>She covers her ears with both hands and looks away.</t>
+          <t>They cover their ears with both hands and look away.</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2779,8 +2779,8 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>I grumbled, and even though she still had her ears
-covered, she answered me.</t>
+          <t>I grumbled, and even though they still had their ears
+covered, they answered me.</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2795,8 +2795,8 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>It’s proof that she can hear me just fine, but at the
-same time I can feel a strong, willful refusal.</t>
+          <t>It’s proof that they can hear me just fine, but at
+the same time I can feel a strong, willful refusal.</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, smooch…」</t>
+          <t>Mmm, smooch…</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>To distract her from the tooth, I sucked my lips to
+          <t>To distract her from the tooth, he sucked his lips to
 hers even more.</t>
         </is>
       </c>
@@ -4032,7 +4032,7 @@
       <c r="B235" s="1" t="inlineStr">
         <is>
           <t>Then Rin-chan answered back with a sweet breath and
-returned it to me.</t>
+returned it to him.</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4138,7 +4138,7 @@
       <c r="B242" s="1" t="inlineStr">
         <is>
           <t>Just as it was turning into their usual kissing,
-Rin-chan sulked and glared at me.</t>
+Rin-chan sulked and glared at him.</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4153,8 +4153,8 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>I still had in mind that the kiss was supposedly to
-pull the tooth out, so I wondered what it meant.</t>
+          <t>He still had in mind that the kiss was supposedly to
+pull the tooth out, so he wondered what it meant.</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>But if I thought about it another way, maybe it was
+          <t>But if he thought about it another way, maybe it was
 better to just keep kissing for now.</t>
         </is>
       </c>
@@ -4581,7 +4581,7 @@
       <c r="B271" s="1" t="inlineStr">
         <is>
           <t>When their tongues met, Rin-chan twisted hers around
-mine like she was asking for it.</t>
+his like she was asking for it.</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... guuguu！ Niini... l-let me down！」</t>
+          <t>Ugh... guuguu！ Niini... l-let me down！</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>「Kuh... kuuuuuuh...！」</t>
+          <t>Kuh... kuuuuuuh...！</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="B411" s="1" t="inlineStr">
         <is>
-          <t>「Hah... hehe！ It's so tight...」</t>
+          <t>Hah... hehe！ It's so tight...</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t>She practically clings to my lips, soft enough to
+          <t>They practically cling to my lips, soft enough to
 make them swell.</t>
         </is>
       </c>
@@ -7968,7 +7968,7 @@
       <c r="B492" s="1" t="inlineStr">
         <is>
           <t>Her wetness pours out, thick and sticky, and clings
-to my penis.</t>
+to his penis.</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8105,8 +8105,8 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>As I thrust upward in time with my words, my penis
-gouges at the inside of her vagina.</t>
+          <t>As he thrusts upward in time with his words, his
+penis gouges at the inside of her vagina.</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="B512" s="1" t="inlineStr">
         <is>
-          <t>「Alright, here I go… mwah！」</t>
+          <t>Alright, here I go… mwah！</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -8302,8 +8302,8 @@
       </c>
       <c r="B514" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nnnh！ Nhaa...！ Nnff！ Nnff... Fuha, haa...
-Nnaaahhh...！」</t>
+          <t>Nn！ Nnnh！ Nhaa...！ Nnff！ Nnff... Fuha, haa...
+Nnaaahhh...！</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -8318,8 +8318,8 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>This time, after properly announcing it, she gently
-presses her tongue against it.</t>
+          <t>This time, after properly announcing it, they gently
+press their tongue against it.</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>「Afa...！ Don't lick my face... no...」</t>
+          <t>Afa...！ Don't lick my face... no...</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>Then, I use the tip of my tongue to knead at the
+          <t>Then, he uses the tip of his tongue to knead at the
 little baby tooth that's about to come loose...</t>
         </is>
       </c>
@@ -9074,8 +9074,8 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>「Ha, fau... ah！ Rin's pussy—it's squeezing so
-tight...！」</t>
+          <t>Ha, fau... ah！ Rin's pussy—it's squeezing so
+tight...！</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>When my penis arched up hard inside her, she
+          <t>When his penis arched up hard inside her, she
 responded exactly as it should...</t>
         </is>
       </c>
@@ -10455,7 +10455,7 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin #Female</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>「Wow... this side got all naughty too, huh？」</t>
+          <t>Wow... this side got all naughty too, huh？</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="B723" s="1" t="inlineStr">
         <is>
-          <t>Is she thanking me too...？</t>
+          <t>Is she thanking me too...？"</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -11631,8 +11631,8 @@
       </c>
       <c r="B730" s="1" t="inlineStr">
         <is>
-          <t>「Did my plan to turn you on and jerk you off while
-making you feel good work?」</t>
+          <t>Did my plan to turn you on and jerk you off while
+making you feel good work?</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="B736" s="1" t="inlineStr">
         <is>
-          <t>「Heh... fine, I'll let it be that way.」</t>
+          <t>Heh... fine, I'll let it be that way.</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... haha！」</t>
+          <t>Ahaha... haha！</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="B773" s="1" t="inlineStr">
         <is>
-          <t>「Taha, tahahaha...！」</t>
+          <t>Taha, tahahaha...！</t>
         </is>
       </c>
       <c r="C773" t="n">
